--- a/artfynd/A 64683-2023 artfynd.xlsx
+++ b/artfynd/A 64683-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 64683-2023 artfynd.xlsx
+++ b/artfynd/A 64683-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4455,6 +4455,122 @@
       <c r="AY35" t="inlineStr">
         <is>
           <t>Kalkbarrianerna 2023, Gotland</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>120337214</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91203</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Västringe, Västringe, Gtl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>708678</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6361839</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Etelhem</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Laritza Pettersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Laritza Pettersson, Peter Frosch</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Kalkbarrianerna 2023, 2024, Gotland</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 64683-2023 artfynd.xlsx
+++ b/artfynd/A 64683-2023 artfynd.xlsx
@@ -4460,7 +4460,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120337214</v>
+        <v>120337052</v>
       </c>
       <c r="B36" t="n">
         <v>91203</v>
@@ -4535,7 +4535,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 64683-2023 artfynd.xlsx
+++ b/artfynd/A 64683-2023 artfynd.xlsx
@@ -4460,7 +4460,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120337052</v>
+        <v>120337214</v>
       </c>
       <c r="B36" t="n">
         <v>91203</v>
@@ -4535,7 +4535,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD36" t="b">
